--- a/delay_pdf/11be/fix_nsta30_CwdsxQSRCxPSRC_sweep_poisson/param_sensitivity_p99_1Mbps.xlsx
+++ b/delay_pdf/11be/fix_nsta30_CwdsxQSRCxPSRC_sweep_poisson/param_sensitivity_p99_1Mbps.xlsx
@@ -660,13 +660,13 @@
         <v>0</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>18224.9</v>
+        <v>19976.7</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>18314.8</v>
+        <v>20087</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
@@ -689,13 +689,13 @@
         <v>0</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>12141.1</v>
+        <v>13813.6</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>20558.6</v>
+        <v>22367.2</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.553</v>
+        <v>0.504</v>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
@@ -718,13 +718,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>17807.9</v>
+        <v>19378.1</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>18740.6</v>
+        <v>20489</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>0.043</v>
+        <v>0.1</v>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
@@ -747,13 +747,13 @@
         <v>0</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>16387.9</v>
+        <v>18131</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>16489.6</v>
+        <v>18183.8</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0.108</v>
+        <v>0.039</v>
       </c>
       <c r="G6" s="16" t="inlineStr">
         <is>
@@ -776,13 +776,13 @@
         <v>5</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>16247.5</v>
+        <v>17790.4</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>16641.2</v>
+        <v>18532.9</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>-0.229</v>
+        <v>-0.295</v>
       </c>
       <c r="G7" s="16" t="inlineStr">
         <is>
@@ -802,16 +802,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>16361</v>
+        <v>18044</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>16535.8</v>
+        <v>18282.7</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0.101</v>
+        <v>0.06</v>
       </c>
       <c r="G8" s="16" t="inlineStr">
         <is>
@@ -1105,22 +1105,22 @@
         <v>0</v>
       </c>
       <c r="B5" s="13" t="n">
-        <v>18224.9</v>
+        <v>19976.7</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>5342.5</v>
+        <v>6517.5</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>26457.5</v>
+        <v>31517.5</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>15643.3</v>
+        <v>16734.2</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>18372.5</v>
+        <v>20306.9</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>20658.9</v>
+        <v>22888.9</v>
       </c>
       <c r="H5" s="21" t="n">
         <v>108</v>
@@ -1136,22 +1136,22 @@
         <v>1</v>
       </c>
       <c r="B6" s="24" t="n">
-        <v>18314.8</v>
+        <v>20087</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>5072.5</v>
+        <v>7277.5</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>28627.5</v>
+        <v>31547.5</v>
       </c>
       <c r="E6" s="24" t="n">
-        <v>16030.3</v>
+        <v>17554.4</v>
       </c>
       <c r="F6" s="24" t="n">
-        <v>18634.2</v>
+        <v>19680.8</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>20280</v>
+        <v>23025.8</v>
       </c>
       <c r="H6" s="25" t="n">
         <v>108</v>
@@ -1161,7 +1161,7 @@
     <row r="7">
       <c r="A7" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.010   |   no clear trend (≈flat)   |   recommended CWds = 0 (lowest mean P99 = 18225 µs)</t>
+          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.012   |   no clear trend (≈flat)   |   recommended CWds = 0 (lowest mean P99 = 19977 µs)</t>
         </is>
       </c>
     </row>
@@ -1220,22 +1220,22 @@
         <v>0</v>
       </c>
       <c r="B11" s="13" t="n">
-        <v>12141.1</v>
+        <v>13813.6</v>
       </c>
       <c r="C11" s="14" t="n">
-        <v>5072.5</v>
+        <v>6517.5</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>16752.5</v>
+        <v>18102.5</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>10099.2</v>
+        <v>11616.7</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>13019.2</v>
+        <v>14320</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>13305</v>
+        <v>15504.2</v>
       </c>
       <c r="H11" s="21" t="n">
         <v>36</v>
@@ -1251,22 +1251,22 @@
         <v>1</v>
       </c>
       <c r="B12" s="24" t="n">
-        <v>16511.1</v>
+        <v>18796.7</v>
       </c>
       <c r="C12" s="24" t="n">
-        <v>12192.5</v>
+        <v>15887.5</v>
       </c>
       <c r="D12" s="24" t="n">
-        <v>21307.5</v>
+        <v>25287.5</v>
       </c>
       <c r="E12" s="24" t="n">
-        <v>14185.8</v>
+        <v>16234.2</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>17201.7</v>
+        <v>18610</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>18145.8</v>
+        <v>21545.8</v>
       </c>
       <c r="H12" s="25" t="n">
         <v>36</v>
@@ -1278,22 +1278,22 @@
         <v>2</v>
       </c>
       <c r="B13" s="29" t="n">
-        <v>20485.8</v>
+        <v>22367.2</v>
       </c>
       <c r="C13" s="29" t="n">
-        <v>15597.5</v>
+        <v>16382.5</v>
       </c>
       <c r="D13" s="29" t="n">
-        <v>28627.5</v>
+        <v>31547.5</v>
       </c>
       <c r="E13" s="29" t="n">
-        <v>16872.5</v>
+        <v>17711.7</v>
       </c>
       <c r="F13" s="29" t="n">
-        <v>20011.7</v>
+        <v>21758.3</v>
       </c>
       <c r="G13" s="29" t="n">
-        <v>24573.3</v>
+        <v>27631.7</v>
       </c>
       <c r="H13" s="30" t="n">
         <v>36</v>
@@ -1305,22 +1305,22 @@
         <v>3</v>
       </c>
       <c r="B14" s="24" t="n">
-        <v>20558.6</v>
+        <v>21950.3</v>
       </c>
       <c r="C14" s="24" t="n">
-        <v>15602.5</v>
+        <v>16397.5</v>
       </c>
       <c r="D14" s="24" t="n">
-        <v>26002.5</v>
+        <v>29812.5</v>
       </c>
       <c r="E14" s="24" t="n">
-        <v>18348.3</v>
+        <v>18343.3</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>20355.8</v>
+        <v>21722.5</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>22971.7</v>
+        <v>25785</v>
       </c>
       <c r="H14" s="25" t="n">
         <v>36</v>
@@ -1332,22 +1332,22 @@
         <v>4</v>
       </c>
       <c r="B15" s="29" t="n">
-        <v>20215.8</v>
+        <v>21710.8</v>
       </c>
       <c r="C15" s="29" t="n">
-        <v>16402.5</v>
+        <v>17637.5</v>
       </c>
       <c r="D15" s="29" t="n">
-        <v>26457.5</v>
+        <v>25842.5</v>
       </c>
       <c r="E15" s="29" t="n">
-        <v>17826.7</v>
+        <v>19452.5</v>
       </c>
       <c r="F15" s="29" t="n">
-        <v>20244.2</v>
+        <v>21899.2</v>
       </c>
       <c r="G15" s="29" t="n">
-        <v>22576.7</v>
+        <v>23780.8</v>
       </c>
       <c r="H15" s="30" t="n">
         <v>36</v>
@@ -1359,22 +1359,22 @@
         <v>5</v>
       </c>
       <c r="B16" s="24" t="n">
-        <v>19706.7</v>
+        <v>21552.5</v>
       </c>
       <c r="C16" s="24" t="n">
-        <v>16597.5</v>
+        <v>18127.5</v>
       </c>
       <c r="D16" s="24" t="n">
-        <v>24507.5</v>
+        <v>26807.5</v>
       </c>
       <c r="E16" s="24" t="n">
-        <v>17688.3</v>
+        <v>19507.5</v>
       </c>
       <c r="F16" s="24" t="n">
-        <v>20187.5</v>
+        <v>21653.3</v>
       </c>
       <c r="G16" s="24" t="n">
-        <v>21244.2</v>
+        <v>23496.7</v>
       </c>
       <c r="H16" s="25" t="n">
         <v>36</v>
@@ -1384,7 +1384,7 @@
     <row r="17">
       <c r="A17" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.553   |   strongly: larger param → larger delay   |   recommended QSRC = 0 (lowest mean P99 = 12141 µs)</t>
+          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.504   |   strongly: larger param → larger delay   |   recommended QSRC = 0 (lowest mean P99 = 13814 µs)</t>
         </is>
       </c>
     </row>
@@ -1443,22 +1443,22 @@
         <v>1</v>
       </c>
       <c r="B21" s="13" t="n">
-        <v>17807.9</v>
+        <v>19378.1</v>
       </c>
       <c r="C21" s="14" t="n">
-        <v>15277.5</v>
+        <v>16397.5</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>20892.5</v>
+        <v>23697.5</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>16244.2</v>
+        <v>17687.1</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>17951.7</v>
+        <v>19191.2</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>19227.9</v>
+        <v>21255.8</v>
       </c>
       <c r="H21" s="21" t="n">
         <v>72</v>
@@ -1474,22 +1474,22 @@
         <v>2</v>
       </c>
       <c r="B22" s="24" t="n">
-        <v>18740.6</v>
+        <v>20228.5</v>
       </c>
       <c r="C22" s="24" t="n">
-        <v>9522.5</v>
+        <v>11302.5</v>
       </c>
       <c r="D22" s="24" t="n">
-        <v>26187.5</v>
+        <v>28737.5</v>
       </c>
       <c r="E22" s="24" t="n">
-        <v>16076.2</v>
+        <v>16895.4</v>
       </c>
       <c r="F22" s="24" t="n">
-        <v>18378.8</v>
+        <v>19907.9</v>
       </c>
       <c r="G22" s="24" t="n">
-        <v>21766.7</v>
+        <v>23882.1</v>
       </c>
       <c r="H22" s="25" t="n">
         <v>72</v>
@@ -1501,22 +1501,22 @@
         <v>3</v>
       </c>
       <c r="B23" s="29" t="n">
-        <v>18261.1</v>
+        <v>20489</v>
       </c>
       <c r="C23" s="29" t="n">
-        <v>5072.5</v>
+        <v>6517.5</v>
       </c>
       <c r="D23" s="29" t="n">
-        <v>28627.5</v>
+        <v>31547.5</v>
       </c>
       <c r="E23" s="29" t="n">
-        <v>15190</v>
+        <v>16850.4</v>
       </c>
       <c r="F23" s="29" t="n">
-        <v>19179.6</v>
+        <v>20882.5</v>
       </c>
       <c r="G23" s="29" t="n">
-        <v>20413.8</v>
+        <v>23734.2</v>
       </c>
       <c r="H23" s="30" t="n">
         <v>72</v>
@@ -1526,7 +1526,7 @@
     <row r="24">
       <c r="A24" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.043   |   no clear trend (≈flat)   |   recommended PSRC = 1 (lowest mean P99 = 17808 µs)</t>
+          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.100   |   no clear trend (≈flat)   |   recommended PSRC = 1 (lowest mean P99 = 19378 µs)</t>
         </is>
       </c>
     </row>
@@ -1626,19 +1626,19 @@
         <v>0</v>
       </c>
       <c r="B5" s="13" t="n">
-        <v>16387.9</v>
+        <v>18131</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>14977.5</v>
+        <v>16597.5</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>17402.5</v>
+        <v>19922.5</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>16259.2</v>
+        <v>17678.6</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>16516.7</v>
+        <v>18583.3</v>
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
@@ -1659,19 +1659,19 @@
         <v>1</v>
       </c>
       <c r="B6" s="24" t="n">
-        <v>16489.6</v>
+        <v>18183.8</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>15557.5</v>
+        <v>16832.5</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>17607.5</v>
+        <v>19242.5</v>
       </c>
       <c r="E6" s="24" t="n">
-        <v>16251.4</v>
+        <v>18091.4</v>
       </c>
       <c r="F6" s="24" t="n">
-        <v>16727.8</v>
+        <v>18276.1</v>
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
     <row r="7">
       <c r="A7" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.108   |   no clear trend (≈flat)   |   recommended CWds = 0 (lowest mean P99 = 16388 µs)</t>
+          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.039   |   no clear trend (≈flat)   |   recommended CWds = 0 (lowest mean P99 = 18131 µs)</t>
         </is>
       </c>
     </row>
@@ -1745,19 +1745,19 @@
         <v>0</v>
       </c>
       <c r="B11" s="29" t="n">
-        <v>16471.2</v>
+        <v>18532.9</v>
       </c>
       <c r="C11" s="29" t="n">
-        <v>16087.5</v>
+        <v>17502.5</v>
       </c>
       <c r="D11" s="29" t="n">
-        <v>16972.5</v>
+        <v>19062.5</v>
       </c>
       <c r="E11" s="29" t="n">
-        <v>16555.8</v>
+        <v>18456.7</v>
       </c>
       <c r="F11" s="29" t="n">
-        <v>16386.7</v>
+        <v>18609.2</v>
       </c>
       <c r="G11" s="29" t="inlineStr">
         <is>
@@ -1774,19 +1774,19 @@
         <v>1</v>
       </c>
       <c r="B12" s="24" t="n">
-        <v>16584.6</v>
+        <v>18370.8</v>
       </c>
       <c r="C12" s="24" t="n">
-        <v>14977.5</v>
+        <v>17602.5</v>
       </c>
       <c r="D12" s="24" t="n">
-        <v>17112.5</v>
+        <v>18962.5</v>
       </c>
       <c r="E12" s="24" t="n">
-        <v>16336.7</v>
+        <v>18194.2</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>16832.5</v>
+        <v>18547.5</v>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
@@ -1803,19 +1803,19 @@
         <v>2</v>
       </c>
       <c r="B13" s="29" t="n">
-        <v>16641.2</v>
+        <v>18103.3</v>
       </c>
       <c r="C13" s="29" t="n">
-        <v>15937.5</v>
+        <v>16857.5</v>
       </c>
       <c r="D13" s="29" t="n">
-        <v>17607.5</v>
+        <v>19922.5</v>
       </c>
       <c r="E13" s="29" t="n">
-        <v>16459.2</v>
+        <v>18005</v>
       </c>
       <c r="F13" s="29" t="n">
-        <v>16823.3</v>
+        <v>18201.7</v>
       </c>
       <c r="G13" s="29" t="inlineStr">
         <is>
@@ -1832,19 +1832,19 @@
         <v>3</v>
       </c>
       <c r="B14" s="24" t="n">
-        <v>16380.4</v>
+        <v>17828.8</v>
       </c>
       <c r="C14" s="24" t="n">
-        <v>15747.5</v>
+        <v>16597.5</v>
       </c>
       <c r="D14" s="24" t="n">
-        <v>17122.5</v>
+        <v>19147.5</v>
       </c>
       <c r="E14" s="24" t="n">
-        <v>16208.3</v>
+        <v>17282.5</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>16552.5</v>
+        <v>18375</v>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
@@ -1861,19 +1861,19 @@
         <v>4</v>
       </c>
       <c r="B15" s="29" t="n">
-        <v>16307.5</v>
+        <v>18317.9</v>
       </c>
       <c r="C15" s="29" t="n">
-        <v>15747.5</v>
+        <v>17077.5</v>
       </c>
       <c r="D15" s="29" t="n">
-        <v>17042.5</v>
+        <v>19242.5</v>
       </c>
       <c r="E15" s="29" t="n">
-        <v>16015</v>
+        <v>17965.8</v>
       </c>
       <c r="F15" s="29" t="n">
-        <v>16600</v>
+        <v>18670</v>
       </c>
       <c r="G15" s="29" t="inlineStr">
         <is>
@@ -1890,19 +1890,19 @@
         <v>5</v>
       </c>
       <c r="B16" s="13" t="n">
-        <v>16247.5</v>
+        <v>17790.4</v>
       </c>
       <c r="C16" s="14" t="n">
-        <v>15557.5</v>
+        <v>16982.5</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>17132.5</v>
+        <v>19107.5</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>15956.7</v>
+        <v>17405.8</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>16538.3</v>
+        <v>18175</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
     <row r="17">
       <c r="A17" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   → Pearson corr(level, P99) = -0.229   |   mildly: smaller param → larger delay   |   recommended QSRC = 5 (lowest mean P99 = 16248 µs)</t>
+          <t xml:space="preserve">   → Pearson corr(level, P99) = -0.295   |   mildly: smaller param → larger delay   |   recommended QSRC = 5 (lowest mean P99 = 17790 µs)</t>
         </is>
       </c>
     </row>
@@ -1976,85 +1976,85 @@
       <c r="I20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="28" t="n">
+      <c r="A21" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="B21" s="29" t="n">
-        <v>16419.4</v>
-      </c>
-      <c r="C21" s="29" t="n">
-        <v>15787.5</v>
-      </c>
-      <c r="D21" s="29" t="n">
-        <v>17187.5</v>
-      </c>
-      <c r="E21" s="29" t="n">
-        <v>16252.1</v>
-      </c>
-      <c r="F21" s="29" t="n">
-        <v>16586.7</v>
-      </c>
-      <c r="G21" s="29" t="inlineStr">
+      <c r="B21" s="13" t="n">
+        <v>18044</v>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>16832.5</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>18937.5</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>17836.7</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>18251.2</v>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H21" s="30" t="n">
+      <c r="H21" s="21" t="n">
         <v>48</v>
       </c>
-      <c r="I21" s="31" t="inlineStr"/>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>◀ best (min P99)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="n">
+      <c r="A22" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B22" s="13" t="n">
-        <v>16361</v>
-      </c>
-      <c r="C22" s="14" t="n">
-        <v>14977.5</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>17132.5</v>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>16112.5</v>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>16609.6</v>
-      </c>
-      <c r="G22" s="14" t="inlineStr">
+      <c r="B22" s="24" t="n">
+        <v>18282.7</v>
+      </c>
+      <c r="C22" s="24" t="n">
+        <v>16982.5</v>
+      </c>
+      <c r="D22" s="24" t="n">
+        <v>19922.5</v>
+      </c>
+      <c r="E22" s="24" t="n">
+        <v>18040.8</v>
+      </c>
+      <c r="F22" s="24" t="n">
+        <v>18524.6</v>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H22" s="21" t="n">
+      <c r="H22" s="25" t="n">
         <v>48</v>
       </c>
-      <c r="I22" s="22" t="inlineStr">
-        <is>
-          <t>◀ best (min P99)</t>
-        </is>
-      </c>
+      <c r="I22" s="26" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="28" t="n">
         <v>3</v>
       </c>
       <c r="B23" s="29" t="n">
-        <v>16535.8</v>
+        <v>18145.4</v>
       </c>
       <c r="C23" s="29" t="n">
-        <v>15992.5</v>
+        <v>16597.5</v>
       </c>
       <c r="D23" s="29" t="n">
-        <v>17607.5</v>
+        <v>19127.5</v>
       </c>
       <c r="E23" s="29" t="n">
-        <v>16401.2</v>
+        <v>17777.5</v>
       </c>
       <c r="F23" s="29" t="n">
-        <v>16670.4</v>
+        <v>18513.3</v>
       </c>
       <c r="G23" s="29" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
     <row r="24">
       <c r="A24" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.101   |   no clear trend (≈flat)   |   recommended PSRC = 2 (lowest mean P99 = 16361 µs)</t>
+          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.060   |   no clear trend (≈flat)   |   recommended PSRC = 1 (lowest mean P99 = 18044 µs)</t>
         </is>
       </c>
     </row>
